--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,6 +690,22 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>signal.uplink_feedback_seconds</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>接入状态行里上一条反馈(已接入 / 已离开 / 拒绝 / 取消 / 核心固件发动)显示多久(真实秒),FG1-SIG-03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -694,13 +694,77 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
+          <t>camera.uplink_zoom_min</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>设置:接入时镜头距离(正交半高倍率)下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>camera.uplink_zoom_max</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>设置:接入时镜头距离(正交半高倍率)上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>camera.uplink_follow_min</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>设置:接入时镜头跟随力度(平滑系数倍率)下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>camera.uplink_follow_max</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>设置:接入时镜头跟随力度(平滑系数倍率)上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>signal.uplink_feedback_seconds</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C21" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>接入状态行里上一条反馈(已接入 / 已离开 / 拒绝 / 取消 / 核心固件发动)显示多久(真实秒),FG1-SIG-03</t>
         </is>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -770,6 +770,182 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>reaction.popup_per_second</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>同一屏幕每秒最多新开几条反应 / 读法弹字(真实秒),FGR-FW-043 初值 6;超出的次数攒着,名额空出来再放</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>reaction.popup_life_seconds</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>弹字最后一次被合并后还停留多久(真实秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>reaction.popup_max_life_seconds</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>同一条弹字最多合并多久(真实秒),持续触发时到点换一条新的</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>reaction.popup_pool</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>同时存在的弹字条数上限(界面标签池大小)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>reaction.popup_height</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>弹字离地高度(米)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>reaction.slowmo_seconds</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>反应第一次触发时的慢放时长(真实秒,暂停时不流逝),FGR-FW-043 初值 0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>reaction.slowmo_factor</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>慢放期间世界推进速度倍率(乘在当前倍速上;只改节奏不改每步 dt,结果与不慢放一致)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>reaction.nudge_seconds</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>反应第一次触发时镜头轻推的时长(真实秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>reaction.nudge_fraction</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>镜头轻推的最大偏移(正交视野半高的比例)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>reaction.log_capacity</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>反应日志保留条数(本次会话,不存档),FGR-FW-043 初值 50</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>reaction.attribution_sessions</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>伤害归因保留最近几场远征 / 突袭(存档),超出丢最旧的已结束场次</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,6 +946,54 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>env.night_brightness_min</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>设置:夜间亮度下限的最小值(夜里画面最暗是白天的20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>env.night_brightness_max</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>设置:夜间亮度下限的最大值(100%=夜里画面不变暗)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>env.night_brightness_default</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>设置:夜间亮度下限的默认值(FGR-ENV-003 保证可读性)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -994,6 +994,54 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>env.silent_dim_min</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>设置:静默夜画面压暗强度的最小值(5% = 几乎不额外压暗;表检查要求界面调参为正数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>env.silent_dim_max</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>设置:静默夜画面压暗强度的最大值(在昼夜亮度之上再暗 60%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>env.silent_dim_default</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>设置:静默夜画面压暗强度的默认值</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,54 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>env.weather_fx_min</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>设置:天气视觉效果强度的最小值(10% = 几乎看不到雨沙雪与沙暴雾;表检查要求界面调参为正数)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>env.weather_fx_max</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>设置:天气视觉效果强度的最大值</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>env.weather_fx_default</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>设置:天气视觉效果强度的默认值</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
+++ b/Configs/GameConfig/Datas/fg/#UiTuning-界面调参.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1090,6 +1090,150 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>narrative.text_speed_min</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>设置:文本显示速度的最小值(每真实秒显示几个字;演出字幕逐字出现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>narrative.text_speed_max</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>120</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>设置:文本显示速度的最大值(拉到最大 = 整行立即出现)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>narrative.text_speed_default</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>40</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>设置:文本显示速度的默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>narrative.subtitle_scale_min</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>设置:字幕大小的最小值(乘在演出字幕与资料库正文的基准字号上)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>narrative.subtitle_scale_max</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>设置:字幕大小的最大值</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>narrative.subtitle_scale_default</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>设置:字幕大小的默认值</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>narrative.subtitle_font_px</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>24</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>演出字幕的基准字号(像素,乘字幕大小)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>narrative.library_font_px</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>14</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>资料库正文的基准字号(像素,乘字幕大小)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>narrative.fallback_hold_seconds</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>演出没有字幕行时(表坏了的兜底)把正文当一行,打完后停留多少真实秒</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
